--- a/v03.xlsx
+++ b/v03.xlsx
@@ -5,12 +5,13 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\3b1b53ad-f5e3-41fe-8f14-0d44a52616ec\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\9da9746c-e37d-42f7-9afe-763929a2622e\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE66A2E1-7459-419B-AAE9-7238AA60950D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DC34F43-2C27-4889-9180-3312A6EC6DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection workbookPassword="C085" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" tabRatio="601"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" tabRatio="601" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -19,12 +20,17 @@
     <sheet name="Sheet4" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet5" sheetId="7" r:id="rId5"/>
     <sheet name="Sheet6" sheetId="9" r:id="rId6"/>
+    <sheet name="Sheet7" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Company">Sheet1!$D$10</definedName>
+    <definedName name="CurrCode_ref">Sheet7!$R$6:$R$184</definedName>
     <definedName name="Date1">Sheet1!$D$11</definedName>
     <definedName name="Date2">Sheet1!$F$11</definedName>
+    <definedName name="Loan_ref" localSheetId="6">Sheet7!$Q$6:$Q$9</definedName>
+    <definedName name="LTV_ref">Sheet7!$T$6:$T$22</definedName>
     <definedName name="Name">Sheet1!$B$8</definedName>
+    <definedName name="Norm_ref">Sheet7!$S$6:$S$7</definedName>
     <definedName name="x13V3_AmSinglBorR">Sheet1!$D$15</definedName>
     <definedName name="x13V3_MagnN3">Sheet1!$C$32</definedName>
     <definedName name="xV3_AddCapDedInc">Sheet2!$F$8</definedName>
@@ -39,6 +45,12 @@
     <definedName name="xV3_GrAddCap">Sheet2!$C$8</definedName>
     <definedName name="xV3_GrFixCap">Sheet2!$B$8</definedName>
     <definedName name="xV3_GrTotCap">Sheet2!$D$8</definedName>
+    <definedName name="xV3_LTV_Loan_Curr">Sheet7!$C$5</definedName>
+    <definedName name="xV3_LTV_Loan_N5">Sheet7!$D$5</definedName>
+    <definedName name="xV3_LTV_Loan_Qt">Sheet7!$G$5</definedName>
+    <definedName name="xV3_LTV_Loan_Ratio">Sheet7!$E$5</definedName>
+    <definedName name="xV3_LTV_Loan_Sum">Sheet7!$F$5</definedName>
+    <definedName name="xV3_LTV_Loan_Type">Sheet7!$B$5</definedName>
     <definedName name="xV3_NormAddCap">Sheet2!$J$8</definedName>
     <definedName name="xV3_NormFixCap">Sheet2!$H$8</definedName>
     <definedName name="xV3_NormGrAddCap">Sheet2!$I$8</definedName>
@@ -85,11 +97,19 @@
     <definedName name="xV3_RWA110Acc">Sheet3!$Q$7</definedName>
     <definedName name="xV3_RWA150Acc">Sheet3!$S$7</definedName>
     <definedName name="xV3_RWA225Acc">Sheet3!$U$7</definedName>
+    <definedName name="yV3_Acc_Dev_AMD">Sheet1!$F$49</definedName>
+    <definedName name="yV3_Acc_Dev_Curr">Sheet1!$F$50</definedName>
     <definedName name="yV3_Cur_10DayVar">Sheet6!$C$10</definedName>
     <definedName name="yV3_Cur_ExcDaysVar">Sheet6!$D$10</definedName>
     <definedName name="yV3_Cur_G">Sheet6!$E$10</definedName>
     <definedName name="yV3_Cur_Risk">Sheet6!$F$10</definedName>
+    <definedName name="yV3_Fact_Dev_AMD">Sheet1!$E$49</definedName>
+    <definedName name="yV3_Fact_Dev_Curr">Sheet1!$E$50</definedName>
+    <definedName name="yV3_FactQt_UnstL_AMD">Sheet1!$D$49</definedName>
+    <definedName name="yV3_FactQt_UnstL_Curr">Sheet1!$D$50</definedName>
     <definedName name="yV3_MagnN11">Sheet1!$B$33</definedName>
+    <definedName name="yV3_PrevAvg_AMD">Sheet1!$C$49</definedName>
+    <definedName name="yV3_PrevAvg_Curr">Sheet1!$C$50</definedName>
     <definedName name="yV3_Ratio">Sheet1!$E$16</definedName>
     <definedName name="yV3_RWA">Sheet1!$C$16</definedName>
   </definedNames>
@@ -112,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="304">
   <si>
     <t>ÜáñÙ³ïÇíÝ»ñÇ Ñ³ßí³ñÏÇ Ù»ç ÁÝ¹·ñÏíáÕ ÙÇçÇÝ óáõó³ÝÇßÝ»ñÇ Ñ³ßí³ñÏÁ</t>
   </si>
@@ -376,10 +396,812 @@
 +(13-14)*100%)+(15-16)*110%)+(17-18) *150%)+(19-20)*225%)</t>
   </si>
   <si>
-    <t>2011_October</t>
-  </si>
-  <si>
     <t>èÇëÏÇ 225% ÏßÇé</t>
+  </si>
+  <si>
+    <r>
+      <t>Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ¨ Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">  ÝáñÙ³ïÇíÝ»ñ</t>
+    </r>
+  </si>
+  <si>
+    <t>²ñÅáõÛÃ</t>
+  </si>
+  <si>
+    <t>Ü³Ëáñ¹ »ñÏáõ »é³ÙëÛ³ÏÝ»ñÇ ÙÇçÇÝ</t>
+  </si>
+  <si>
+    <r>
+      <t>ºé³ÙëÛ³ÏÇ ÁÝÃ³óùáõÙ ÷³ëï³óÇ ïñ³Ù³¹ñí³Í ¨ Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ÝáñÙ³ïÇíÝ»ñÇÝ ãµ³í³ñ³ñáÕ í³ñÏ»ñ</t>
+    </r>
+  </si>
+  <si>
+    <t>ö³ëï³óÇ ß»ÕáõÙ</t>
+  </si>
+  <si>
+    <t>ÂáõÛÉ³ïñ»ÉÇ ß»ÕáõÙ</t>
+  </si>
+  <si>
+    <t>ÐÐ ¹ñ³Ù</t>
+  </si>
+  <si>
+    <t>²ñï³ñÅáõÛÃ</t>
+  </si>
+  <si>
+    <r>
+      <t>Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ¨ Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="12"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> ÝáñÙ³ïÇíÝ»ñÇ Ñ³ßí³ñÏÇ Ù»ç ÁÝ¹·ñÏíáÕ óáõó³ÝÇßÝ»ñÇ í»ñ³µ»ñÛ³É</t>
+    </r>
+  </si>
+  <si>
+    <t>Ð/Ñ</t>
+  </si>
+  <si>
+    <t>Üáñ ïñ³Ù³¹ñíáÕ í³ñÏÇ ï»ë³Ï</t>
+  </si>
+  <si>
+    <t>Üáñ ïñ³Ù³¹ñíáÕ í³ñÏÇ ³ñÅáõÛÃ</t>
+  </si>
+  <si>
+    <t>ÜáñÙ³ïÇíÇ ï»ë³Ï</t>
+  </si>
+  <si>
+    <t>ä³Ñ³ÝçÇ ¨ ·ñ³íÇ ³ñÅ»ùÇ Ñ³ñ³µ»ñ³Ïóáõ-ÃÛáõÝ</t>
+  </si>
+  <si>
+    <t>Üáñ ïñ³Ù³¹ñíáÕ í³ñÏÇ Ù³Ûñ ·áõÙ³ñ</t>
+  </si>
+  <si>
+    <t>ø³Ý³Ï</t>
+  </si>
+  <si>
+    <t>Ò»éùµ»ñÙ³Ý í³ñÏ</t>
+  </si>
+  <si>
+    <t>Î³éáõóÙ³Ý/í»ñ³Ï³éáõóÙ³Ý í³ñÏ</t>
+  </si>
+  <si>
+    <t>ì»ñ³Ýáñá·Ù³Ý í³ñÏ</t>
+  </si>
+  <si>
+    <t>²Ýß³ñÅ ·áõÛùáí ³å³Ñáíí³Í ³ÛÉ í³ñÏ</t>
+  </si>
+  <si>
+    <t>Loan_ref</t>
+  </si>
+  <si>
+    <t>CurrCode_ref</t>
+  </si>
+  <si>
+    <t>Norm_ref</t>
+  </si>
+  <si>
+    <t>LTV_ref</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>[0%-10%]</t>
+  </si>
+  <si>
+    <t>AFN</t>
+  </si>
+  <si>
+    <t>(10%-20%]</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>(20%-30%]</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>(30%-40%]</t>
+  </si>
+  <si>
+    <t>ANG</t>
+  </si>
+  <si>
+    <t>(40%-50%]</t>
+  </si>
+  <si>
+    <t>AOA</t>
+  </si>
+  <si>
+    <t>(50%-60%]</t>
+  </si>
+  <si>
+    <t>ARS</t>
+  </si>
+  <si>
+    <t>(60%-65%]</t>
+  </si>
+  <si>
+    <t>AUD</t>
+  </si>
+  <si>
+    <t>(65%-70%]</t>
+  </si>
+  <si>
+    <t>AWG</t>
+  </si>
+  <si>
+    <t>(70%-75%]</t>
+  </si>
+  <si>
+    <t>AZN</t>
+  </si>
+  <si>
+    <t>(75%-80%]</t>
+  </si>
+  <si>
+    <t>BAM</t>
+  </si>
+  <si>
+    <t>(80%-85%]</t>
+  </si>
+  <si>
+    <t>BBD</t>
+  </si>
+  <si>
+    <t>(85%-90%]</t>
+  </si>
+  <si>
+    <t>BDT</t>
+  </si>
+  <si>
+    <t>(90%-95%]</t>
+  </si>
+  <si>
+    <t>BGN</t>
+  </si>
+  <si>
+    <t>(95%-100%]</t>
+  </si>
+  <si>
+    <t>BHD</t>
+  </si>
+  <si>
+    <t>(100%-120%]</t>
+  </si>
+  <si>
+    <t>BIF</t>
+  </si>
+  <si>
+    <t>(120%-150%]</t>
+  </si>
+  <si>
+    <t>BMD</t>
+  </si>
+  <si>
+    <t>&gt;150</t>
+  </si>
+  <si>
+    <t>BND</t>
+  </si>
+  <si>
+    <t>BOB</t>
+  </si>
+  <si>
+    <t>BOV</t>
+  </si>
+  <si>
+    <t>BRL</t>
+  </si>
+  <si>
+    <t>BSD</t>
+  </si>
+  <si>
+    <t>BTN</t>
+  </si>
+  <si>
+    <t>BWP</t>
+  </si>
+  <si>
+    <t>BYN</t>
+  </si>
+  <si>
+    <t>BZD</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>CDF</t>
+  </si>
+  <si>
+    <t>CHE</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>CHW</t>
+  </si>
+  <si>
+    <t>CLF</t>
+  </si>
+  <si>
+    <t>CLP</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>COU</t>
+  </si>
+  <si>
+    <t>CRC</t>
+  </si>
+  <si>
+    <t>CUC</t>
+  </si>
+  <si>
+    <t>CUP</t>
+  </si>
+  <si>
+    <t>CVE</t>
+  </si>
+  <si>
+    <t>CZK</t>
+  </si>
+  <si>
+    <t>DJF</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>DOP</t>
+  </si>
+  <si>
+    <t>DZD</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>ERN</t>
+  </si>
+  <si>
+    <t>ETB</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>FJD</t>
+  </si>
+  <si>
+    <t>FKP</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>GEL</t>
+  </si>
+  <si>
+    <t>GHS</t>
+  </si>
+  <si>
+    <t>GIP</t>
+  </si>
+  <si>
+    <t>GMD</t>
+  </si>
+  <si>
+    <t>GNF</t>
+  </si>
+  <si>
+    <t>GTQ</t>
+  </si>
+  <si>
+    <t>GYD</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>HNL</t>
+  </si>
+  <si>
+    <t>HRK</t>
+  </si>
+  <si>
+    <t>HTG</t>
+  </si>
+  <si>
+    <t>HUF</t>
+  </si>
+  <si>
+    <t>IDR</t>
+  </si>
+  <si>
+    <t>ILS</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>IQD</t>
+  </si>
+  <si>
+    <t>IRR</t>
+  </si>
+  <si>
+    <t>ISK</t>
+  </si>
+  <si>
+    <t>JMD</t>
+  </si>
+  <si>
+    <t>JOD</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>KES</t>
+  </si>
+  <si>
+    <t>KGS</t>
+  </si>
+  <si>
+    <t>KHR</t>
+  </si>
+  <si>
+    <t>KMF</t>
+  </si>
+  <si>
+    <t>KPW</t>
+  </si>
+  <si>
+    <t>KRW</t>
+  </si>
+  <si>
+    <t>KWD</t>
+  </si>
+  <si>
+    <t>KYD</t>
+  </si>
+  <si>
+    <t>KZT</t>
+  </si>
+  <si>
+    <t>LAK</t>
+  </si>
+  <si>
+    <t>LBP</t>
+  </si>
+  <si>
+    <t>LKR</t>
+  </si>
+  <si>
+    <t>LRD</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>LYD</t>
+  </si>
+  <si>
+    <t>MAD</t>
+  </si>
+  <si>
+    <t>MDL</t>
+  </si>
+  <si>
+    <t>MGA</t>
+  </si>
+  <si>
+    <t>MKD</t>
+  </si>
+  <si>
+    <t>MMK</t>
+  </si>
+  <si>
+    <t>MNT</t>
+  </si>
+  <si>
+    <t>MOP</t>
+  </si>
+  <si>
+    <t>MRU</t>
+  </si>
+  <si>
+    <t>MUR</t>
+  </si>
+  <si>
+    <t>MVR</t>
+  </si>
+  <si>
+    <t>MWK</t>
+  </si>
+  <si>
+    <t>MXN</t>
+  </si>
+  <si>
+    <t>MXV</t>
+  </si>
+  <si>
+    <t>MYR</t>
+  </si>
+  <si>
+    <t>MZN</t>
+  </si>
+  <si>
+    <t>NAD</t>
+  </si>
+  <si>
+    <t>NGN</t>
+  </si>
+  <si>
+    <t>NIO</t>
+  </si>
+  <si>
+    <t>NOK</t>
+  </si>
+  <si>
+    <t>NPR</t>
+  </si>
+  <si>
+    <t>NZD</t>
+  </si>
+  <si>
+    <t>OMR</t>
+  </si>
+  <si>
+    <t>PAB</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t>PGK</t>
+  </si>
+  <si>
+    <t>PHP</t>
+  </si>
+  <si>
+    <t>PKR</t>
+  </si>
+  <si>
+    <t>PLN</t>
+  </si>
+  <si>
+    <t>PYG</t>
+  </si>
+  <si>
+    <t>QAR</t>
+  </si>
+  <si>
+    <t>RON</t>
+  </si>
+  <si>
+    <t>RSD</t>
+  </si>
+  <si>
+    <t>RUB</t>
+  </si>
+  <si>
+    <t>RWF</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>SBD</t>
+  </si>
+  <si>
+    <t>SCR</t>
+  </si>
+  <si>
+    <t>SDG</t>
+  </si>
+  <si>
+    <t>SEK</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>SHP</t>
+  </si>
+  <si>
+    <t>SLL</t>
+  </si>
+  <si>
+    <t>SOS</t>
+  </si>
+  <si>
+    <t>SRD</t>
+  </si>
+  <si>
+    <t>SSP</t>
+  </si>
+  <si>
+    <t>STN</t>
+  </si>
+  <si>
+    <t>SVC</t>
+  </si>
+  <si>
+    <t>SYP</t>
+  </si>
+  <si>
+    <t>SZL</t>
+  </si>
+  <si>
+    <t>THB</t>
+  </si>
+  <si>
+    <t>TJS</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>TND</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>TRY</t>
+  </si>
+  <si>
+    <t>TTD</t>
+  </si>
+  <si>
+    <t>TWD</t>
+  </si>
+  <si>
+    <t>TZS</t>
+  </si>
+  <si>
+    <t>UAH</t>
+  </si>
+  <si>
+    <t>UGX</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>USN</t>
+  </si>
+  <si>
+    <t>UYI</t>
+  </si>
+  <si>
+    <t>UYU</t>
+  </si>
+  <si>
+    <t>UYW</t>
+  </si>
+  <si>
+    <t>UZS</t>
+  </si>
+  <si>
+    <t>VES</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>VUV</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>XAF</t>
+  </si>
+  <si>
+    <t>XAG</t>
+  </si>
+  <si>
+    <t>XAU</t>
+  </si>
+  <si>
+    <t>XBA</t>
+  </si>
+  <si>
+    <t>XBB</t>
+  </si>
+  <si>
+    <t>XBC</t>
+  </si>
+  <si>
+    <t>XBD</t>
+  </si>
+  <si>
+    <t>XCD</t>
+  </si>
+  <si>
+    <t>XDR</t>
+  </si>
+  <si>
+    <t>XOF</t>
+  </si>
+  <si>
+    <t>XPD</t>
+  </si>
+  <si>
+    <t>XPF</t>
+  </si>
+  <si>
+    <t>XPT</t>
+  </si>
+  <si>
+    <t>XSU</t>
+  </si>
+  <si>
+    <t>XTS</t>
+  </si>
+  <si>
+    <t>XUA</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>YER</t>
+  </si>
+  <si>
+    <t>ZAR</t>
+  </si>
+  <si>
+    <t>ZMW</t>
+  </si>
+  <si>
+    <t>ZWL</t>
+  </si>
+  <si>
+    <t>2022_April</t>
+  </si>
+  <si>
+    <r>
+      <t>Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ü5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color indexed="10"/>
+        <rFont val="Times Armenian"/>
+        <family val="1"/>
+      </rPr>
+      <t>2</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -390,7 +1212,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="173" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="29">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -481,10 +1303,78 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="12"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color indexed="10"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="0"/>
       <name val="Arial Armenian"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="GHEA Grapalat"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times Armenian"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -501,7 +1391,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -1086,10 +1976,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="hair">
         <color indexed="64"/>
       </left>
-      <right style="hair">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1100,7 +2003,20 @@
       <left style="hair">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1154,7 +2070,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
@@ -1162,8 +2078,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="258">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1595,15 +2512,130 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="30" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1616,6 +2648,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1646,7 +2687,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1655,22 +2696,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1690,11 +2731,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1712,11 +2753,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="50" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="Comma 7" xfId="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2"/>
@@ -1724,6 +2768,7 @@
     <cellStyle name="Normal 6" xfId="4"/>
     <cellStyle name="Normal 7" xfId="5"/>
     <cellStyle name="Normal_Sheet3" xfId="6"/>
+    <cellStyle name="Percent" xfId="7" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2087,7 +3132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="19"/>
@@ -2104,7 +3149,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="168" t="s">
-        <v>80</v>
+        <v>301</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="49"/>
@@ -2117,18 +3162,18 @@
       <c r="G2" s="49"/>
     </row>
     <row r="3" spans="1:10" ht="12.75" customHeight="1">
-      <c r="F3" s="170" t="s">
+      <c r="F3" s="210" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="170"/>
-      <c r="H3" s="170"/>
-      <c r="I3" s="170"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="F4" s="170"/>
-      <c r="G4" s="170"/>
-      <c r="H4" s="170"/>
-      <c r="I4" s="170"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="I4" s="210"/>
     </row>
     <row r="5" spans="1:10">
       <c r="F5" s="6"/>
@@ -2336,20 +3381,20 @@
       <c r="I29" s="49"/>
     </row>
     <row r="30" spans="2:9" ht="32.25" customHeight="1">
-      <c r="B30" s="171" t="s">
+      <c r="B30" s="211" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="173" t="s">
+      <c r="C30" s="213" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="175"/>
-      <c r="E30" s="176"/>
+      <c r="D30" s="215"/>
+      <c r="E30" s="216"/>
     </row>
     <row r="31" spans="2:9" ht="30.75" customHeight="1">
-      <c r="B31" s="172"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="175"/>
-      <c r="E31" s="176"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="214"/>
+      <c r="D31" s="215"/>
+      <c r="E31" s="216"/>
     </row>
     <row r="32" spans="2:9">
       <c r="B32" s="82" t="s">
@@ -2498,68 +3543,313 @@
       <c r="C46" s="49"/>
       <c r="D46" s="49"/>
       <c r="E46" s="49"/>
-      <c r="F46" s="49"/>
+      <c r="F46" s="181" t="s">
+        <v>4</v>
+      </c>
       <c r="G46" s="49"/>
       <c r="H46" s="49"/>
       <c r="I46" s="49"/>
     </row>
     <row r="47" spans="2:9">
-      <c r="B47" s="49"/>
-      <c r="D47" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="E47" s="113"/>
-      <c r="F47" s="49"/>
+      <c r="B47" s="217" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="218"/>
+      <c r="D47" s="218"/>
+      <c r="E47" s="218"/>
+      <c r="F47" s="219"/>
       <c r="G47" s="49"/>
       <c r="H47" s="49"/>
       <c r="I47" s="49"/>
     </row>
-    <row r="48" spans="2:9">
-      <c r="D48" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
+    <row r="48" spans="2:9" ht="61.5">
+      <c r="B48" s="170" t="s">
+        <v>82</v>
+      </c>
+      <c r="C48" s="171" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="171" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="171" t="s">
+        <v>85</v>
+      </c>
+      <c r="F48" s="172" t="s">
+        <v>86</v>
+      </c>
       <c r="G48" s="49"/>
       <c r="H48" s="49"/>
       <c r="I48" s="49"/>
     </row>
     <row r="49" spans="2:9">
-      <c r="B49" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="E49" s="113"/>
-      <c r="F49" s="49"/>
+      <c r="B49" s="173" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="174"/>
+      <c r="D49" s="174"/>
+      <c r="E49" s="175" t="e">
+        <f>D49/C49</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F49" s="176"/>
       <c r="G49" s="49"/>
       <c r="H49" s="49"/>
       <c r="I49" s="49"/>
     </row>
     <row r="50" spans="2:9">
-      <c r="B50" s="49"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
+      <c r="B50" s="177" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="178"/>
+      <c r="D50" s="178"/>
+      <c r="E50" s="179" t="e">
+        <f>D50/C50</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F50" s="180"/>
       <c r="G50" s="49"/>
       <c r="H50" s="49"/>
       <c r="I50" s="49"/>
     </row>
     <row r="51" spans="2:9">
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="49"/>
+      <c r="I51" s="49"/>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52" s="49"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="49"/>
+      <c r="I52" s="49"/>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53" s="49"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="49"/>
+      <c r="F53" s="49"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="49"/>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54" s="49"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="49"/>
+      <c r="E54" s="49"/>
+      <c r="F54" s="49"/>
+      <c r="G54" s="49"/>
+      <c r="H54" s="49"/>
+      <c r="I54" s="49"/>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55" s="49"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="49"/>
+    </row>
+    <row r="56" spans="2:9">
+      <c r="B56" s="49"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="49"/>
+      <c r="E56" s="49"/>
+      <c r="F56" s="49"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="49"/>
+    </row>
+    <row r="57" spans="2:9">
+      <c r="B57" s="49"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="49"/>
+      <c r="E57" s="49"/>
+      <c r="F57" s="49"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="49"/>
+    </row>
+    <row r="58" spans="2:9">
+      <c r="B58" s="49"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+      <c r="E58" s="49"/>
+      <c r="F58" s="49"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="49"/>
+    </row>
+    <row r="59" spans="2:9">
+      <c r="B59" s="49"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+    </row>
+    <row r="60" spans="2:9">
+      <c r="B60" s="49"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+      <c r="E60" s="49"/>
+      <c r="F60" s="49"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="49"/>
+    </row>
+    <row r="61" spans="2:9">
+      <c r="B61" s="49"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="49"/>
+      <c r="E61" s="49"/>
+      <c r="F61" s="49"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+    </row>
+    <row r="62" spans="2:9">
+      <c r="B62" s="49"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+    </row>
+    <row r="63" spans="2:9">
+      <c r="B63" s="49"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="49"/>
+      <c r="E63" s="49"/>
+      <c r="F63" s="49"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="49"/>
+    </row>
+    <row r="64" spans="2:9">
+      <c r="B64" s="49"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="49"/>
+      <c r="E64" s="49"/>
+      <c r="F64" s="49"/>
+      <c r="G64" s="49"/>
+      <c r="H64" s="49"/>
+      <c r="I64" s="49"/>
+    </row>
+    <row r="65" spans="2:9">
+      <c r="B65" s="49"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="49"/>
+      <c r="E65" s="49"/>
+      <c r="F65" s="49"/>
+      <c r="G65" s="49"/>
+      <c r="H65" s="49"/>
+      <c r="I65" s="49"/>
+    </row>
+    <row r="66" spans="2:9">
+      <c r="B66" s="49"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="49"/>
+      <c r="E66" s="49"/>
+      <c r="F66" s="49"/>
+      <c r="G66" s="49"/>
+      <c r="H66" s="49"/>
+      <c r="I66" s="49"/>
+    </row>
+    <row r="67" spans="2:9">
+      <c r="B67" s="49"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="49"/>
+      <c r="E67" s="49"/>
+      <c r="F67" s="49"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+    </row>
+    <row r="68" spans="2:9">
+      <c r="B68" s="49"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="49"/>
+      <c r="E68" s="49"/>
+      <c r="F68" s="49"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="49"/>
+      <c r="I68" s="49"/>
+    </row>
+    <row r="69" spans="2:9">
+      <c r="B69" s="49"/>
+      <c r="D69" s="73" t="s">
+        <v>49</v>
+      </c>
+      <c r="E69" s="113"/>
+      <c r="F69" s="49"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="49"/>
+    </row>
+    <row r="70" spans="2:9">
+      <c r="D70" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="E70" s="49"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="49"/>
+      <c r="I70" s="49"/>
+    </row>
+    <row r="71" spans="2:9">
+      <c r="B71" s="47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="113"/>
+      <c r="F71" s="49"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="49"/>
+    </row>
+    <row r="72" spans="2:9">
+      <c r="B72" s="49"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="49"/>
+      <c r="E72" s="49"/>
+      <c r="F72" s="49"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="49"/>
+      <c r="I72" s="49"/>
+    </row>
+    <row r="73" spans="2:9">
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
     </row>
   </sheetData>
   <sheetProtection password="A028" sheet="1"/>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="F3:I4"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D31"/>
     <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B47:F47"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <dataValidations count="1">
@@ -2689,41 +3979,41 @@
       <c r="N5" s="5"/>
     </row>
     <row r="6" spans="1:14" ht="39" customHeight="1">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="225" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="177" t="s">
+      <c r="B6" s="220" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="177" t="s">
+      <c r="C6" s="220" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="177" t="s">
+      <c r="D6" s="220" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="179" t="s">
+      <c r="E6" s="222" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="181" t="s">
+      <c r="F6" s="224" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="181"/>
-      <c r="H6" s="177" t="s">
+      <c r="G6" s="224"/>
+      <c r="H6" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="177"/>
-      <c r="J6" s="177"/>
-      <c r="K6" s="178"/>
+      <c r="I6" s="220"/>
+      <c r="J6" s="220"/>
+      <c r="K6" s="221"/>
       <c r="L6" s="17"/>
       <c r="M6" s="18"/>
       <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14" ht="48">
-      <c r="A7" s="183"/>
-      <c r="B7" s="184"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="180"/>
+      <c r="A7" s="226"/>
+      <c r="B7" s="227"/>
+      <c r="C7" s="227"/>
+      <c r="D7" s="227"/>
+      <c r="E7" s="223"/>
       <c r="F7" s="85" t="s">
         <v>30</v>
       </c>
@@ -3953,56 +5243,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="97" customFormat="1" ht="15">
-      <c r="A1" s="185" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="185"/>
-      <c r="O1" s="185"/>
-      <c r="P1" s="185"/>
-      <c r="Q1" s="185"/>
-      <c r="R1" s="185"/>
-      <c r="S1" s="185"/>
-      <c r="T1" s="185"/>
-      <c r="U1" s="185"/>
-      <c r="V1" s="185"/>
+      <c r="A1" s="228" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
+      <c r="H1" s="228"/>
+      <c r="I1" s="228"/>
+      <c r="J1" s="228"/>
+      <c r="K1" s="228"/>
+      <c r="L1" s="228"/>
+      <c r="M1" s="228"/>
+      <c r="N1" s="228"/>
+      <c r="O1" s="228"/>
+      <c r="P1" s="228"/>
+      <c r="Q1" s="228"/>
+      <c r="R1" s="228"/>
+      <c r="S1" s="228"/>
+      <c r="T1" s="228"/>
+      <c r="U1" s="228"/>
+      <c r="V1" s="228"/>
     </row>
     <row r="2" spans="1:23" s="97" customFormat="1" ht="15">
-      <c r="A2" s="186" t="s">
+      <c r="A2" s="229" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="186"/>
-      <c r="C2" s="186"/>
-      <c r="D2" s="186"/>
-      <c r="E2" s="186"/>
-      <c r="F2" s="186"/>
-      <c r="G2" s="186"/>
-      <c r="H2" s="186"/>
-      <c r="I2" s="186"/>
-      <c r="J2" s="186"/>
-      <c r="K2" s="186"/>
-      <c r="L2" s="186"/>
-      <c r="M2" s="186"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="186"/>
-      <c r="P2" s="186"/>
-      <c r="Q2" s="186"/>
-      <c r="R2" s="186"/>
-      <c r="S2" s="186"/>
-      <c r="T2" s="186"/>
-      <c r="U2" s="186"/>
-      <c r="V2" s="186"/>
+      <c r="B2" s="229"/>
+      <c r="C2" s="229"/>
+      <c r="D2" s="229"/>
+      <c r="E2" s="229"/>
+      <c r="F2" s="229"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="229"/>
+      <c r="I2" s="229"/>
+      <c r="J2" s="229"/>
+      <c r="K2" s="229"/>
+      <c r="L2" s="229"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="229"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="229"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="229"/>
+      <c r="U2" s="229"/>
+      <c r="V2" s="229"/>
     </row>
     <row r="3" spans="1:23" s="97" customFormat="1" ht="15">
       <c r="A3" s="98"/>
@@ -4029,56 +5319,56 @@
       <c r="V3" s="3"/>
     </row>
     <row r="4" spans="1:23" s="97" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A4" s="187" t="s">
+      <c r="A4" s="230" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="187"/>
-      <c r="C4" s="187"/>
-      <c r="D4" s="187"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="187"/>
-      <c r="H4" s="187"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="187"/>
-      <c r="L4" s="187"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="187"/>
-      <c r="O4" s="187"/>
-      <c r="P4" s="187"/>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="187"/>
-      <c r="S4" s="187"/>
-      <c r="T4" s="187"/>
-      <c r="U4" s="187"/>
-      <c r="V4" s="187"/>
+      <c r="B4" s="230"/>
+      <c r="C4" s="230"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="230"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="230"/>
+      <c r="H4" s="230"/>
+      <c r="I4" s="230"/>
+      <c r="J4" s="230"/>
+      <c r="K4" s="230"/>
+      <c r="L4" s="230"/>
+      <c r="M4" s="230"/>
+      <c r="N4" s="230"/>
+      <c r="O4" s="230"/>
+      <c r="P4" s="230"/>
+      <c r="Q4" s="230"/>
+      <c r="R4" s="230"/>
+      <c r="S4" s="230"/>
+      <c r="T4" s="230"/>
+      <c r="U4" s="230"/>
+      <c r="V4" s="230"/>
     </row>
     <row r="5" spans="1:23" s="100" customFormat="1" ht="28.5" customHeight="1">
-      <c r="A5" s="188" t="s">
+      <c r="A5" s="231" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="189"/>
-      <c r="C5" s="189"/>
-      <c r="D5" s="189"/>
-      <c r="E5" s="189"/>
-      <c r="F5" s="189"/>
-      <c r="G5" s="189"/>
-      <c r="H5" s="189"/>
-      <c r="I5" s="189"/>
-      <c r="J5" s="189"/>
-      <c r="K5" s="189"/>
-      <c r="L5" s="189"/>
-      <c r="M5" s="189"/>
-      <c r="N5" s="189"/>
-      <c r="O5" s="189"/>
-      <c r="P5" s="190"/>
-      <c r="Q5" s="190"/>
-      <c r="R5" s="190"/>
-      <c r="S5" s="190"/>
-      <c r="T5" s="190"/>
-      <c r="U5" s="190"/>
-      <c r="V5" s="191"/>
+      <c r="B5" s="232"/>
+      <c r="C5" s="232"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
+      <c r="M5" s="232"/>
+      <c r="N5" s="232"/>
+      <c r="O5" s="232"/>
+      <c r="P5" s="233"/>
+      <c r="Q5" s="233"/>
+      <c r="R5" s="233"/>
+      <c r="S5" s="233"/>
+      <c r="T5" s="233"/>
+      <c r="U5" s="233"/>
+      <c r="V5" s="234"/>
       <c r="W5" s="99"/>
     </row>
     <row r="6" spans="1:23" s="97" customFormat="1" ht="86.25" customHeight="1">
@@ -5461,56 +6751,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A1" s="199" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="199"/>
-      <c r="C1" s="199"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="199"/>
-      <c r="G1" s="199"/>
-      <c r="H1" s="199"/>
-      <c r="I1" s="199"/>
-      <c r="J1" s="199"/>
-      <c r="K1" s="199"/>
-      <c r="L1" s="199"/>
-      <c r="M1" s="199"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="199"/>
-      <c r="P1" s="199"/>
-      <c r="Q1" s="199"/>
-      <c r="R1" s="199"/>
-      <c r="S1" s="199"/>
-      <c r="T1" s="199"/>
-      <c r="U1" s="199"/>
-      <c r="V1" s="199"/>
+      <c r="A1" s="242" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="242"/>
+      <c r="I1" s="242"/>
+      <c r="J1" s="242"/>
+      <c r="K1" s="242"/>
+      <c r="L1" s="242"/>
+      <c r="M1" s="242"/>
+      <c r="N1" s="242"/>
+      <c r="O1" s="242"/>
+      <c r="P1" s="242"/>
+      <c r="Q1" s="242"/>
+      <c r="R1" s="242"/>
+      <c r="S1" s="242"/>
+      <c r="T1" s="242"/>
+      <c r="U1" s="242"/>
+      <c r="V1" s="242"/>
     </row>
     <row r="2" spans="1:22" ht="15">
-      <c r="A2" s="200" t="s">
+      <c r="A2" s="243" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="200"/>
-      <c r="I2" s="200"/>
-      <c r="J2" s="200"/>
-      <c r="K2" s="200"/>
-      <c r="L2" s="200"/>
-      <c r="M2" s="200"/>
-      <c r="N2" s="200"/>
-      <c r="O2" s="200"/>
-      <c r="P2" s="200"/>
-      <c r="Q2" s="200"/>
-      <c r="R2" s="200"/>
-      <c r="S2" s="200"/>
-      <c r="T2" s="200"/>
-      <c r="U2" s="200"/>
-      <c r="V2" s="200"/>
+      <c r="B2" s="243"/>
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="243"/>
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="50"/>
@@ -5536,56 +6826,56 @@
       <c r="U3" s="19"/>
     </row>
     <row r="4" spans="1:22" ht="18.75" customHeight="1">
-      <c r="A4" s="192" t="s">
+      <c r="A4" s="235" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="193"/>
-      <c r="C4" s="193"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
-      <c r="K4" s="193"/>
-      <c r="L4" s="193"/>
-      <c r="M4" s="193"/>
-      <c r="N4" s="193"/>
-      <c r="O4" s="193"/>
-      <c r="P4" s="194"/>
-      <c r="Q4" s="194"/>
-      <c r="R4" s="194"/>
-      <c r="S4" s="194"/>
-      <c r="T4" s="194"/>
-      <c r="U4" s="194"/>
-      <c r="V4" s="194"/>
+      <c r="B4" s="236"/>
+      <c r="C4" s="236"/>
+      <c r="D4" s="236"/>
+      <c r="E4" s="236"/>
+      <c r="F4" s="236"/>
+      <c r="G4" s="236"/>
+      <c r="H4" s="236"/>
+      <c r="I4" s="236"/>
+      <c r="J4" s="236"/>
+      <c r="K4" s="236"/>
+      <c r="L4" s="236"/>
+      <c r="M4" s="236"/>
+      <c r="N4" s="236"/>
+      <c r="O4" s="236"/>
+      <c r="P4" s="237"/>
+      <c r="Q4" s="237"/>
+      <c r="R4" s="237"/>
+      <c r="S4" s="237"/>
+      <c r="T4" s="237"/>
+      <c r="U4" s="237"/>
+      <c r="V4" s="237"/>
     </row>
     <row r="5" spans="1:22" ht="27.75" customHeight="1">
-      <c r="A5" s="195" t="s">
+      <c r="A5" s="238" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
-      <c r="F5" s="196"/>
-      <c r="G5" s="196"/>
-      <c r="H5" s="196"/>
-      <c r="I5" s="196"/>
-      <c r="J5" s="196"/>
-      <c r="K5" s="196"/>
-      <c r="L5" s="196"/>
-      <c r="M5" s="196"/>
-      <c r="N5" s="196"/>
-      <c r="O5" s="196"/>
-      <c r="P5" s="197"/>
-      <c r="Q5" s="197"/>
-      <c r="R5" s="197"/>
-      <c r="S5" s="197"/>
-      <c r="T5" s="197"/>
-      <c r="U5" s="197"/>
-      <c r="V5" s="198"/>
+      <c r="B5" s="239"/>
+      <c r="C5" s="239"/>
+      <c r="D5" s="239"/>
+      <c r="E5" s="239"/>
+      <c r="F5" s="239"/>
+      <c r="G5" s="239"/>
+      <c r="H5" s="239"/>
+      <c r="I5" s="239"/>
+      <c r="J5" s="239"/>
+      <c r="K5" s="239"/>
+      <c r="L5" s="239"/>
+      <c r="M5" s="239"/>
+      <c r="N5" s="239"/>
+      <c r="O5" s="239"/>
+      <c r="P5" s="240"/>
+      <c r="Q5" s="240"/>
+      <c r="R5" s="240"/>
+      <c r="S5" s="240"/>
+      <c r="T5" s="240"/>
+      <c r="U5" s="240"/>
+      <c r="V5" s="241"/>
     </row>
     <row r="6" spans="1:22" ht="102" customHeight="1">
       <c r="A6" s="108" t="s">
@@ -5646,7 +6936,7 @@
         <v>36</v>
       </c>
       <c r="T6" s="109" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="U6" s="109" t="s">
         <v>36</v>
@@ -6789,22 +8079,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="15">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="228" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="15">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
+      <c r="A2" s="228"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
     </row>
     <row r="3" spans="1:6" s="6" customFormat="1">
       <c r="A3" s="16"/>
@@ -6815,42 +8105,42 @@
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" s="6" customFormat="1" ht="15">
-      <c r="A4" s="201" t="s">
+      <c r="A4" s="244" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="202"/>
-      <c r="C4" s="202"/>
-      <c r="D4" s="202"/>
-      <c r="E4" s="202"/>
-      <c r="F4" s="203"/>
+      <c r="B4" s="245"/>
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="246"/>
     </row>
     <row r="5" spans="1:6" s="6" customFormat="1">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="247" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="206" t="s">
+      <c r="B5" s="249" t="s">
         <v>56</v>
       </c>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="249" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="206" t="s">
+      <c r="D5" s="249" t="s">
         <v>58</v>
       </c>
-      <c r="E5" s="206" t="s">
+      <c r="E5" s="249" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="206" t="s">
+      <c r="F5" s="249" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="205"/>
-      <c r="B6" s="207"/>
-      <c r="C6" s="207"/>
-      <c r="D6" s="207"/>
-      <c r="E6" s="207"/>
-      <c r="F6" s="207"/>
+      <c r="A6" s="248"/>
+      <c r="B6" s="250"/>
+      <c r="C6" s="250"/>
+      <c r="D6" s="250"/>
+      <c r="E6" s="250"/>
+      <c r="F6" s="250"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="133"/>
@@ -7415,22 +8705,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="6" customFormat="1" ht="15">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="228" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
+      <c r="B1" s="228"/>
+      <c r="C1" s="228"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
     </row>
     <row r="2" spans="1:6" s="6" customFormat="1" ht="15">
-      <c r="A2" s="185"/>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
+      <c r="A2" s="228"/>
+      <c r="B2" s="228"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
     </row>
     <row r="3" spans="1:6" s="6" customFormat="1" ht="15.75">
       <c r="A3" s="128"/>
@@ -7443,32 +8733,32 @@
       <c r="F3" s="128"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="209" t="s">
+      <c r="A7" s="252" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="208" t="s">
+      <c r="B7" s="251" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="211" t="s">
+      <c r="C7" s="254" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="212" t="s">
+      <c r="D7" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="208" t="s">
+      <c r="E7" s="251" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="208" t="s">
+      <c r="F7" s="251" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26.25" customHeight="1">
-      <c r="A8" s="210"/>
-      <c r="B8" s="208"/>
-      <c r="C8" s="211"/>
-      <c r="D8" s="213"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
+      <c r="A8" s="253"/>
+      <c r="B8" s="251"/>
+      <c r="C8" s="254"/>
+      <c r="D8" s="256"/>
+      <c r="E8" s="251"/>
+      <c r="F8" s="251"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="150"/>
@@ -7841,4 +9131,2049 @@
     <ignoredError sqref="B41" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:BV184"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="7" width="20.42578125" customWidth="1"/>
+    <col min="8" max="16" width="9.140625" style="204"/>
+    <col min="17" max="17" width="39.7109375" style="205" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="205" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" style="205" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="205" hidden="1" customWidth="1"/>
+    <col min="21" max="74" width="9.140625" style="204"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="18.75">
+      <c r="A1" s="257" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="257"/>
+      <c r="C1" s="257"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+    </row>
+    <row r="2" spans="1:20" ht="15">
+      <c r="A2" s="182"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="182"/>
+      <c r="G2" s="201"/>
+    </row>
+    <row r="3" spans="1:20" ht="15">
+      <c r="A3" s="182"/>
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="182"/>
+      <c r="E3" s="182"/>
+      <c r="F3" s="182"/>
+      <c r="G3" s="202"/>
+    </row>
+    <row r="4" spans="1:20" ht="24">
+      <c r="A4" s="183" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="184" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="184" t="s">
+        <v>92</v>
+      </c>
+      <c r="D4" s="184" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="184" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="184" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="185" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="186"/>
+      <c r="B5" s="203">
+        <v>1</v>
+      </c>
+      <c r="C5" s="187">
+        <v>2</v>
+      </c>
+      <c r="D5" s="187">
+        <v>3</v>
+      </c>
+      <c r="E5" s="187">
+        <v>4</v>
+      </c>
+      <c r="F5" s="187">
+        <v>5</v>
+      </c>
+      <c r="G5" s="188">
+        <v>6</v>
+      </c>
+      <c r="Q5" s="206" t="s">
+        <v>101</v>
+      </c>
+      <c r="R5" s="206" t="s">
+        <v>102</v>
+      </c>
+      <c r="S5" s="206" t="s">
+        <v>103</v>
+      </c>
+      <c r="T5" s="206" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="18">
+      <c r="A6" s="189">
+        <v>1</v>
+      </c>
+      <c r="B6" s="190"/>
+      <c r="C6" s="190"/>
+      <c r="D6" s="190"/>
+      <c r="E6" s="190"/>
+      <c r="F6" s="191"/>
+      <c r="G6" s="192"/>
+      <c r="P6" s="207"/>
+      <c r="Q6" s="208" t="s">
+        <v>97</v>
+      </c>
+      <c r="R6" s="208" t="s">
+        <v>105</v>
+      </c>
+      <c r="S6" s="208" t="s">
+        <v>302</v>
+      </c>
+      <c r="T6" s="208" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="18">
+      <c r="A7" s="193">
+        <v>2</v>
+      </c>
+      <c r="B7" s="194"/>
+      <c r="C7" s="194"/>
+      <c r="D7" s="194"/>
+      <c r="E7" s="194"/>
+      <c r="F7" s="195"/>
+      <c r="G7" s="196"/>
+      <c r="P7" s="207"/>
+      <c r="Q7" s="208" t="s">
+        <v>98</v>
+      </c>
+      <c r="R7" s="208" t="s">
+        <v>107</v>
+      </c>
+      <c r="S7" s="208" t="s">
+        <v>303</v>
+      </c>
+      <c r="T7" s="208" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="15">
+      <c r="A8" s="193">
+        <v>3</v>
+      </c>
+      <c r="B8" s="194"/>
+      <c r="C8" s="194"/>
+      <c r="D8" s="194"/>
+      <c r="E8" s="194"/>
+      <c r="F8" s="195"/>
+      <c r="G8" s="196"/>
+      <c r="P8" s="207"/>
+      <c r="Q8" s="208" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" s="208" t="s">
+        <v>109</v>
+      </c>
+      <c r="S8" s="209"/>
+      <c r="T8" s="208" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="15">
+      <c r="A9" s="193">
+        <v>4</v>
+      </c>
+      <c r="B9" s="194"/>
+      <c r="C9" s="194"/>
+      <c r="D9" s="194"/>
+      <c r="E9" s="194"/>
+      <c r="F9" s="195"/>
+      <c r="G9" s="196"/>
+      <c r="P9" s="207"/>
+      <c r="Q9" s="208" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="208" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="209"/>
+      <c r="T9" s="208" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15">
+      <c r="A10" s="193">
+        <v>5</v>
+      </c>
+      <c r="B10" s="194"/>
+      <c r="C10" s="194"/>
+      <c r="D10" s="194"/>
+      <c r="E10" s="194"/>
+      <c r="F10" s="195"/>
+      <c r="G10" s="196"/>
+      <c r="P10" s="207"/>
+      <c r="Q10" s="209"/>
+      <c r="R10" s="209" t="s">
+        <v>113</v>
+      </c>
+      <c r="S10" s="209"/>
+      <c r="T10" s="208" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15">
+      <c r="A11" s="193">
+        <v>6</v>
+      </c>
+      <c r="B11" s="194"/>
+      <c r="C11" s="194"/>
+      <c r="D11" s="194"/>
+      <c r="E11" s="194"/>
+      <c r="F11" s="195"/>
+      <c r="G11" s="196"/>
+      <c r="P11" s="207"/>
+      <c r="Q11" s="209"/>
+      <c r="R11" s="209" t="s">
+        <v>115</v>
+      </c>
+      <c r="S11" s="209"/>
+      <c r="T11" s="208" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="15">
+      <c r="A12" s="193">
+        <v>7</v>
+      </c>
+      <c r="B12" s="194"/>
+      <c r="C12" s="194"/>
+      <c r="D12" s="194"/>
+      <c r="E12" s="194"/>
+      <c r="F12" s="195"/>
+      <c r="G12" s="196"/>
+      <c r="P12" s="207"/>
+      <c r="Q12" s="209"/>
+      <c r="R12" s="209" t="s">
+        <v>117</v>
+      </c>
+      <c r="S12" s="209"/>
+      <c r="T12" s="208" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="15">
+      <c r="A13" s="193">
+        <v>8</v>
+      </c>
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
+      <c r="F13" s="195"/>
+      <c r="G13" s="196"/>
+      <c r="P13" s="207"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="209" t="s">
+        <v>119</v>
+      </c>
+      <c r="S13" s="209"/>
+      <c r="T13" s="208" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="15">
+      <c r="A14" s="193">
+        <v>9</v>
+      </c>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
+      <c r="F14" s="195"/>
+      <c r="G14" s="196"/>
+      <c r="P14" s="207"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="209" t="s">
+        <v>121</v>
+      </c>
+      <c r="S14" s="209"/>
+      <c r="T14" s="208" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="15">
+      <c r="A15" s="193">
+        <v>10</v>
+      </c>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
+      <c r="F15" s="195"/>
+      <c r="G15" s="196"/>
+      <c r="P15" s="207"/>
+      <c r="Q15" s="209"/>
+      <c r="R15" s="209" t="s">
+        <v>123</v>
+      </c>
+      <c r="S15" s="209"/>
+      <c r="T15" s="208" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="15">
+      <c r="A16" s="193">
+        <v>11</v>
+      </c>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
+      <c r="F16" s="195"/>
+      <c r="G16" s="196"/>
+      <c r="P16" s="207"/>
+      <c r="Q16" s="209"/>
+      <c r="R16" s="209" t="s">
+        <v>125</v>
+      </c>
+      <c r="S16" s="209"/>
+      <c r="T16" s="208" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="15">
+      <c r="A17" s="193">
+        <v>12</v>
+      </c>
+      <c r="B17" s="194"/>
+      <c r="C17" s="194"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
+      <c r="G17" s="196"/>
+      <c r="P17" s="207"/>
+      <c r="Q17" s="209"/>
+      <c r="R17" s="209" t="s">
+        <v>127</v>
+      </c>
+      <c r="S17" s="209"/>
+      <c r="T17" s="208" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="15">
+      <c r="A18" s="193">
+        <v>13</v>
+      </c>
+      <c r="B18" s="194"/>
+      <c r="C18" s="194"/>
+      <c r="D18" s="194"/>
+      <c r="E18" s="194"/>
+      <c r="F18" s="195"/>
+      <c r="G18" s="196"/>
+      <c r="P18" s="207"/>
+      <c r="Q18" s="209"/>
+      <c r="R18" s="209" t="s">
+        <v>129</v>
+      </c>
+      <c r="S18" s="209"/>
+      <c r="T18" s="208" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="15">
+      <c r="A19" s="193">
+        <v>14</v>
+      </c>
+      <c r="B19" s="194"/>
+      <c r="C19" s="194"/>
+      <c r="D19" s="194"/>
+      <c r="E19" s="194"/>
+      <c r="F19" s="195"/>
+      <c r="G19" s="196"/>
+      <c r="P19" s="207"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="209" t="s">
+        <v>131</v>
+      </c>
+      <c r="S19" s="209"/>
+      <c r="T19" s="208" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="15">
+      <c r="A20" s="193">
+        <v>15</v>
+      </c>
+      <c r="B20" s="194"/>
+      <c r="C20" s="194"/>
+      <c r="D20" s="194"/>
+      <c r="E20" s="194"/>
+      <c r="F20" s="195"/>
+      <c r="G20" s="196"/>
+      <c r="P20" s="207"/>
+      <c r="Q20" s="209"/>
+      <c r="R20" s="209" t="s">
+        <v>133</v>
+      </c>
+      <c r="S20" s="209"/>
+      <c r="T20" s="208" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="15">
+      <c r="A21" s="193">
+        <v>16</v>
+      </c>
+      <c r="B21" s="194"/>
+      <c r="C21" s="194"/>
+      <c r="D21" s="194"/>
+      <c r="E21" s="194"/>
+      <c r="F21" s="195"/>
+      <c r="G21" s="196"/>
+      <c r="P21" s="207"/>
+      <c r="Q21" s="209"/>
+      <c r="R21" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="S21" s="209"/>
+      <c r="T21" s="208" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="15">
+      <c r="A22" s="193">
+        <v>17</v>
+      </c>
+      <c r="B22" s="194"/>
+      <c r="C22" s="194"/>
+      <c r="D22" s="194"/>
+      <c r="E22" s="194"/>
+      <c r="F22" s="195"/>
+      <c r="G22" s="196"/>
+      <c r="P22" s="207"/>
+      <c r="Q22" s="209"/>
+      <c r="R22" s="209" t="s">
+        <v>137</v>
+      </c>
+      <c r="S22" s="209"/>
+      <c r="T22" s="208" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
+      <c r="A23" s="193">
+        <v>18</v>
+      </c>
+      <c r="B23" s="194"/>
+      <c r="C23" s="194"/>
+      <c r="D23" s="194"/>
+      <c r="E23" s="194"/>
+      <c r="F23" s="195"/>
+      <c r="G23" s="196"/>
+      <c r="P23" s="207"/>
+      <c r="Q23" s="209"/>
+      <c r="R23" s="209" t="s">
+        <v>139</v>
+      </c>
+      <c r="S23" s="209"/>
+      <c r="T23" s="209"/>
+    </row>
+    <row r="24" spans="1:20">
+      <c r="A24" s="193">
+        <v>19</v>
+      </c>
+      <c r="B24" s="194"/>
+      <c r="C24" s="194"/>
+      <c r="D24" s="194"/>
+      <c r="E24" s="194"/>
+      <c r="F24" s="195"/>
+      <c r="G24" s="196"/>
+      <c r="P24" s="207"/>
+      <c r="Q24" s="209"/>
+      <c r="R24" s="209" t="s">
+        <v>140</v>
+      </c>
+      <c r="S24" s="209"/>
+      <c r="T24" s="209"/>
+    </row>
+    <row r="25" spans="1:20">
+      <c r="A25" s="193">
+        <v>20</v>
+      </c>
+      <c r="B25" s="194"/>
+      <c r="C25" s="194"/>
+      <c r="D25" s="194"/>
+      <c r="E25" s="194"/>
+      <c r="F25" s="195"/>
+      <c r="G25" s="196"/>
+      <c r="P25" s="207"/>
+      <c r="Q25" s="209"/>
+      <c r="R25" s="209" t="s">
+        <v>141</v>
+      </c>
+      <c r="S25" s="209"/>
+      <c r="T25" s="209"/>
+    </row>
+    <row r="26" spans="1:20">
+      <c r="A26" s="193">
+        <v>21</v>
+      </c>
+      <c r="B26" s="194"/>
+      <c r="C26" s="194"/>
+      <c r="D26" s="194"/>
+      <c r="E26" s="194"/>
+      <c r="F26" s="195"/>
+      <c r="G26" s="196"/>
+      <c r="R26" s="205" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
+      <c r="A27" s="193">
+        <v>22</v>
+      </c>
+      <c r="B27" s="194"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="195"/>
+      <c r="G27" s="196"/>
+      <c r="R27" s="205" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
+      <c r="A28" s="193">
+        <v>23</v>
+      </c>
+      <c r="B28" s="194"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="194"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="195"/>
+      <c r="G28" s="196"/>
+      <c r="R28" s="205" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
+      <c r="A29" s="193">
+        <v>24</v>
+      </c>
+      <c r="B29" s="194"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="194"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="195"/>
+      <c r="G29" s="196"/>
+      <c r="R29" s="205" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="193">
+        <v>25</v>
+      </c>
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="195"/>
+      <c r="G30" s="196"/>
+      <c r="R30" s="205" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
+      <c r="A31" s="193">
+        <v>26</v>
+      </c>
+      <c r="B31" s="194"/>
+      <c r="C31" s="194"/>
+      <c r="D31" s="194"/>
+      <c r="E31" s="194"/>
+      <c r="F31" s="195"/>
+      <c r="G31" s="196"/>
+      <c r="R31" s="205" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
+      <c r="A32" s="193">
+        <v>27</v>
+      </c>
+      <c r="B32" s="194"/>
+      <c r="C32" s="194"/>
+      <c r="D32" s="194"/>
+      <c r="E32" s="194"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="196"/>
+      <c r="R32" s="205" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
+      <c r="A33" s="193">
+        <v>28</v>
+      </c>
+      <c r="B33" s="194"/>
+      <c r="C33" s="194"/>
+      <c r="D33" s="194"/>
+      <c r="E33" s="194"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="196"/>
+      <c r="R33" s="205" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="193">
+        <v>29</v>
+      </c>
+      <c r="B34" s="194"/>
+      <c r="C34" s="194"/>
+      <c r="D34" s="194"/>
+      <c r="E34" s="194"/>
+      <c r="F34" s="195"/>
+      <c r="G34" s="196"/>
+      <c r="R34" s="205" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="193">
+        <v>30</v>
+      </c>
+      <c r="B35" s="194"/>
+      <c r="C35" s="194"/>
+      <c r="D35" s="194"/>
+      <c r="E35" s="194"/>
+      <c r="F35" s="195"/>
+      <c r="G35" s="196"/>
+      <c r="R35" s="205" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="193">
+        <v>31</v>
+      </c>
+      <c r="B36" s="194"/>
+      <c r="C36" s="194"/>
+      <c r="D36" s="194"/>
+      <c r="E36" s="194"/>
+      <c r="F36" s="195"/>
+      <c r="G36" s="196"/>
+      <c r="R36" s="205" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="193">
+        <v>32</v>
+      </c>
+      <c r="B37" s="194"/>
+      <c r="C37" s="194"/>
+      <c r="D37" s="194"/>
+      <c r="E37" s="194"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="196"/>
+      <c r="R37" s="205" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
+      <c r="A38" s="193">
+        <v>33</v>
+      </c>
+      <c r="B38" s="194"/>
+      <c r="C38" s="194"/>
+      <c r="D38" s="194"/>
+      <c r="E38" s="194"/>
+      <c r="F38" s="195"/>
+      <c r="G38" s="196"/>
+      <c r="R38" s="205" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
+      <c r="A39" s="193">
+        <v>34</v>
+      </c>
+      <c r="B39" s="194"/>
+      <c r="C39" s="194"/>
+      <c r="D39" s="194"/>
+      <c r="E39" s="194"/>
+      <c r="F39" s="195"/>
+      <c r="G39" s="196"/>
+      <c r="R39" s="205" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
+      <c r="A40" s="193">
+        <v>35</v>
+      </c>
+      <c r="B40" s="194"/>
+      <c r="C40" s="194"/>
+      <c r="D40" s="194"/>
+      <c r="E40" s="194"/>
+      <c r="F40" s="195"/>
+      <c r="G40" s="196"/>
+      <c r="R40" s="205" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="A41" s="193">
+        <v>36</v>
+      </c>
+      <c r="B41" s="194"/>
+      <c r="C41" s="194"/>
+      <c r="D41" s="194"/>
+      <c r="E41" s="194"/>
+      <c r="F41" s="195"/>
+      <c r="G41" s="196"/>
+      <c r="R41" s="205" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
+      <c r="A42" s="193">
+        <v>37</v>
+      </c>
+      <c r="B42" s="194"/>
+      <c r="C42" s="194"/>
+      <c r="D42" s="194"/>
+      <c r="E42" s="194"/>
+      <c r="F42" s="195"/>
+      <c r="G42" s="196"/>
+      <c r="R42" s="205" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
+      <c r="A43" s="193">
+        <v>38</v>
+      </c>
+      <c r="B43" s="194"/>
+      <c r="C43" s="194"/>
+      <c r="D43" s="194"/>
+      <c r="E43" s="194"/>
+      <c r="F43" s="195"/>
+      <c r="G43" s="196"/>
+      <c r="R43" s="205" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
+      <c r="A44" s="193">
+        <v>39</v>
+      </c>
+      <c r="B44" s="194"/>
+      <c r="C44" s="194"/>
+      <c r="D44" s="194"/>
+      <c r="E44" s="194"/>
+      <c r="F44" s="195"/>
+      <c r="G44" s="196"/>
+      <c r="R44" s="205" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
+      <c r="A45" s="193">
+        <v>40</v>
+      </c>
+      <c r="B45" s="194"/>
+      <c r="C45" s="194"/>
+      <c r="D45" s="194"/>
+      <c r="E45" s="194"/>
+      <c r="F45" s="195"/>
+      <c r="G45" s="196"/>
+      <c r="R45" s="205" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
+      <c r="A46" s="193">
+        <v>41</v>
+      </c>
+      <c r="B46" s="194"/>
+      <c r="C46" s="194"/>
+      <c r="D46" s="194"/>
+      <c r="E46" s="194"/>
+      <c r="F46" s="195"/>
+      <c r="G46" s="196"/>
+      <c r="R46" s="205" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
+      <c r="A47" s="193">
+        <v>42</v>
+      </c>
+      <c r="B47" s="194"/>
+      <c r="C47" s="194"/>
+      <c r="D47" s="194"/>
+      <c r="E47" s="194"/>
+      <c r="F47" s="195"/>
+      <c r="G47" s="196"/>
+      <c r="R47" s="205" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
+      <c r="A48" s="193">
+        <v>43</v>
+      </c>
+      <c r="B48" s="194"/>
+      <c r="C48" s="194"/>
+      <c r="D48" s="194"/>
+      <c r="E48" s="194"/>
+      <c r="F48" s="195"/>
+      <c r="G48" s="196"/>
+      <c r="R48" s="205" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
+      <c r="A49" s="193">
+        <v>44</v>
+      </c>
+      <c r="B49" s="194"/>
+      <c r="C49" s="194"/>
+      <c r="D49" s="194"/>
+      <c r="E49" s="194"/>
+      <c r="F49" s="195"/>
+      <c r="G49" s="196"/>
+      <c r="R49" s="205" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
+      <c r="A50" s="193">
+        <v>45</v>
+      </c>
+      <c r="B50" s="194"/>
+      <c r="C50" s="194"/>
+      <c r="D50" s="194"/>
+      <c r="E50" s="194"/>
+      <c r="F50" s="195"/>
+      <c r="G50" s="196"/>
+      <c r="R50" s="205" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
+      <c r="A51" s="193">
+        <v>46</v>
+      </c>
+      <c r="B51" s="194"/>
+      <c r="C51" s="194"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="195"/>
+      <c r="G51" s="196"/>
+      <c r="R51" s="205" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
+      <c r="A52" s="193">
+        <v>47</v>
+      </c>
+      <c r="B52" s="194"/>
+      <c r="C52" s="194"/>
+      <c r="D52" s="194"/>
+      <c r="E52" s="194"/>
+      <c r="F52" s="195"/>
+      <c r="G52" s="196"/>
+      <c r="R52" s="205" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
+      <c r="A53" s="193">
+        <v>48</v>
+      </c>
+      <c r="B53" s="194"/>
+      <c r="C53" s="194"/>
+      <c r="D53" s="194"/>
+      <c r="E53" s="194"/>
+      <c r="F53" s="195"/>
+      <c r="G53" s="196"/>
+      <c r="R53" s="205" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
+      <c r="A54" s="193">
+        <v>49</v>
+      </c>
+      <c r="B54" s="194"/>
+      <c r="C54" s="194"/>
+      <c r="D54" s="194"/>
+      <c r="E54" s="194"/>
+      <c r="F54" s="195"/>
+      <c r="G54" s="196"/>
+      <c r="R54" s="205" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
+      <c r="A55" s="193">
+        <v>50</v>
+      </c>
+      <c r="B55" s="194"/>
+      <c r="C55" s="194"/>
+      <c r="D55" s="194"/>
+      <c r="E55" s="194"/>
+      <c r="F55" s="195"/>
+      <c r="G55" s="196"/>
+      <c r="R55" s="205" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
+      <c r="A56" s="193">
+        <v>51</v>
+      </c>
+      <c r="B56" s="194"/>
+      <c r="C56" s="194"/>
+      <c r="D56" s="194"/>
+      <c r="E56" s="194"/>
+      <c r="F56" s="195"/>
+      <c r="G56" s="196"/>
+      <c r="R56" s="205" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
+      <c r="A57" s="193">
+        <v>52</v>
+      </c>
+      <c r="B57" s="194"/>
+      <c r="C57" s="194"/>
+      <c r="D57" s="194"/>
+      <c r="E57" s="194"/>
+      <c r="F57" s="195"/>
+      <c r="G57" s="196"/>
+      <c r="R57" s="205" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
+      <c r="A58" s="193">
+        <v>53</v>
+      </c>
+      <c r="B58" s="194"/>
+      <c r="C58" s="194"/>
+      <c r="D58" s="194"/>
+      <c r="E58" s="194"/>
+      <c r="F58" s="195"/>
+      <c r="G58" s="196"/>
+      <c r="R58" s="205" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
+      <c r="A59" s="193">
+        <v>54</v>
+      </c>
+      <c r="B59" s="194"/>
+      <c r="C59" s="194"/>
+      <c r="D59" s="194"/>
+      <c r="E59" s="194"/>
+      <c r="F59" s="195"/>
+      <c r="G59" s="196"/>
+      <c r="R59" s="205" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
+      <c r="A60" s="193">
+        <v>55</v>
+      </c>
+      <c r="B60" s="194"/>
+      <c r="C60" s="194"/>
+      <c r="D60" s="194"/>
+      <c r="E60" s="194"/>
+      <c r="F60" s="195"/>
+      <c r="G60" s="196"/>
+      <c r="R60" s="205" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
+      <c r="A61" s="193">
+        <v>56</v>
+      </c>
+      <c r="B61" s="194"/>
+      <c r="C61" s="194"/>
+      <c r="D61" s="194"/>
+      <c r="E61" s="194"/>
+      <c r="F61" s="195"/>
+      <c r="G61" s="196"/>
+      <c r="R61" s="205" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
+      <c r="A62" s="193">
+        <v>57</v>
+      </c>
+      <c r="B62" s="194"/>
+      <c r="C62" s="194"/>
+      <c r="D62" s="194"/>
+      <c r="E62" s="194"/>
+      <c r="F62" s="195"/>
+      <c r="G62" s="196"/>
+      <c r="R62" s="205" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
+      <c r="A63" s="193">
+        <v>58</v>
+      </c>
+      <c r="B63" s="194"/>
+      <c r="C63" s="194"/>
+      <c r="D63" s="194"/>
+      <c r="E63" s="194"/>
+      <c r="F63" s="195"/>
+      <c r="G63" s="196"/>
+      <c r="R63" s="205" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
+      <c r="A64" s="193">
+        <v>59</v>
+      </c>
+      <c r="B64" s="194"/>
+      <c r="C64" s="194"/>
+      <c r="D64" s="194"/>
+      <c r="E64" s="194"/>
+      <c r="F64" s="195"/>
+      <c r="G64" s="196"/>
+      <c r="R64" s="205" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
+      <c r="A65" s="193">
+        <v>60</v>
+      </c>
+      <c r="B65" s="194"/>
+      <c r="C65" s="194"/>
+      <c r="D65" s="194"/>
+      <c r="E65" s="194"/>
+      <c r="F65" s="195"/>
+      <c r="G65" s="196"/>
+      <c r="R65" s="205" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
+      <c r="A66" s="193">
+        <v>61</v>
+      </c>
+      <c r="B66" s="194"/>
+      <c r="C66" s="194"/>
+      <c r="D66" s="194"/>
+      <c r="E66" s="194"/>
+      <c r="F66" s="195"/>
+      <c r="G66" s="196"/>
+      <c r="R66" s="205" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
+      <c r="A67" s="193">
+        <v>62</v>
+      </c>
+      <c r="B67" s="194"/>
+      <c r="C67" s="194"/>
+      <c r="D67" s="194"/>
+      <c r="E67" s="194"/>
+      <c r="F67" s="195"/>
+      <c r="G67" s="196"/>
+      <c r="R67" s="205" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
+      <c r="A68" s="193">
+        <v>63</v>
+      </c>
+      <c r="B68" s="194"/>
+      <c r="C68" s="194"/>
+      <c r="D68" s="194"/>
+      <c r="E68" s="194"/>
+      <c r="F68" s="195"/>
+      <c r="G68" s="196"/>
+      <c r="R68" s="205" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="A69" s="193">
+        <v>64</v>
+      </c>
+      <c r="B69" s="194"/>
+      <c r="C69" s="194"/>
+      <c r="D69" s="194"/>
+      <c r="E69" s="194"/>
+      <c r="F69" s="195"/>
+      <c r="G69" s="196"/>
+      <c r="R69" s="205" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="A70" s="193">
+        <v>65</v>
+      </c>
+      <c r="B70" s="194"/>
+      <c r="C70" s="194"/>
+      <c r="D70" s="194"/>
+      <c r="E70" s="194"/>
+      <c r="F70" s="195"/>
+      <c r="G70" s="196"/>
+      <c r="R70" s="205" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="A71" s="193">
+        <v>66</v>
+      </c>
+      <c r="B71" s="194"/>
+      <c r="C71" s="194"/>
+      <c r="D71" s="194"/>
+      <c r="E71" s="194"/>
+      <c r="F71" s="195"/>
+      <c r="G71" s="196"/>
+      <c r="R71" s="205" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="A72" s="193">
+        <v>67</v>
+      </c>
+      <c r="B72" s="194"/>
+      <c r="C72" s="194"/>
+      <c r="D72" s="194"/>
+      <c r="E72" s="194"/>
+      <c r="F72" s="195"/>
+      <c r="G72" s="196"/>
+      <c r="R72" s="205" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="A73" s="193">
+        <v>68</v>
+      </c>
+      <c r="B73" s="194"/>
+      <c r="C73" s="194"/>
+      <c r="D73" s="194"/>
+      <c r="E73" s="194"/>
+      <c r="F73" s="195"/>
+      <c r="G73" s="196"/>
+      <c r="R73" s="205" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="A74" s="193">
+        <v>69</v>
+      </c>
+      <c r="B74" s="194"/>
+      <c r="C74" s="194"/>
+      <c r="D74" s="194"/>
+      <c r="E74" s="194"/>
+      <c r="F74" s="195"/>
+      <c r="G74" s="196"/>
+      <c r="R74" s="205" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="A75" s="193">
+        <v>70</v>
+      </c>
+      <c r="B75" s="194"/>
+      <c r="C75" s="194"/>
+      <c r="D75" s="194"/>
+      <c r="E75" s="194"/>
+      <c r="F75" s="195"/>
+      <c r="G75" s="196"/>
+      <c r="R75" s="205" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="A76" s="193">
+        <v>71</v>
+      </c>
+      <c r="B76" s="194"/>
+      <c r="C76" s="194"/>
+      <c r="D76" s="194"/>
+      <c r="E76" s="194"/>
+      <c r="F76" s="195"/>
+      <c r="G76" s="196"/>
+      <c r="R76" s="205" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="A77" s="193">
+        <v>72</v>
+      </c>
+      <c r="B77" s="194"/>
+      <c r="C77" s="194"/>
+      <c r="D77" s="194"/>
+      <c r="E77" s="194"/>
+      <c r="F77" s="195"/>
+      <c r="G77" s="196"/>
+      <c r="R77" s="205" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="A78" s="193">
+        <v>73</v>
+      </c>
+      <c r="B78" s="194"/>
+      <c r="C78" s="194"/>
+      <c r="D78" s="194"/>
+      <c r="E78" s="194"/>
+      <c r="F78" s="195"/>
+      <c r="G78" s="196"/>
+      <c r="R78" s="205" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="A79" s="193">
+        <v>74</v>
+      </c>
+      <c r="B79" s="194"/>
+      <c r="C79" s="194"/>
+      <c r="D79" s="194"/>
+      <c r="E79" s="194"/>
+      <c r="F79" s="195"/>
+      <c r="G79" s="196"/>
+      <c r="R79" s="205" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
+      <c r="A80" s="193">
+        <v>75</v>
+      </c>
+      <c r="B80" s="194"/>
+      <c r="C80" s="194"/>
+      <c r="D80" s="194"/>
+      <c r="E80" s="194"/>
+      <c r="F80" s="195"/>
+      <c r="G80" s="196"/>
+      <c r="R80" s="205" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
+      <c r="A81" s="193">
+        <v>76</v>
+      </c>
+      <c r="B81" s="194"/>
+      <c r="C81" s="194"/>
+      <c r="D81" s="194"/>
+      <c r="E81" s="194"/>
+      <c r="F81" s="195"/>
+      <c r="G81" s="196"/>
+      <c r="R81" s="205" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
+      <c r="A82" s="193">
+        <v>77</v>
+      </c>
+      <c r="B82" s="194"/>
+      <c r="C82" s="194"/>
+      <c r="D82" s="194"/>
+      <c r="E82" s="194"/>
+      <c r="F82" s="195"/>
+      <c r="G82" s="196"/>
+      <c r="R82" s="205" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
+      <c r="A83" s="193">
+        <v>78</v>
+      </c>
+      <c r="B83" s="194"/>
+      <c r="C83" s="194"/>
+      <c r="D83" s="194"/>
+      <c r="E83" s="194"/>
+      <c r="F83" s="195"/>
+      <c r="G83" s="196"/>
+      <c r="R83" s="205" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
+      <c r="A84" s="193">
+        <v>79</v>
+      </c>
+      <c r="B84" s="194"/>
+      <c r="C84" s="194"/>
+      <c r="D84" s="194"/>
+      <c r="E84" s="194"/>
+      <c r="F84" s="195"/>
+      <c r="G84" s="196"/>
+      <c r="R84" s="205" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
+      <c r="A85" s="193">
+        <v>80</v>
+      </c>
+      <c r="B85" s="194"/>
+      <c r="C85" s="194"/>
+      <c r="D85" s="194"/>
+      <c r="E85" s="194"/>
+      <c r="F85" s="195"/>
+      <c r="G85" s="196"/>
+      <c r="R85" s="205" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
+      <c r="A86" s="193">
+        <v>81</v>
+      </c>
+      <c r="B86" s="194"/>
+      <c r="C86" s="194"/>
+      <c r="D86" s="194"/>
+      <c r="E86" s="194"/>
+      <c r="F86" s="195"/>
+      <c r="G86" s="196"/>
+      <c r="R86" s="205" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
+      <c r="A87" s="193">
+        <v>82</v>
+      </c>
+      <c r="B87" s="194"/>
+      <c r="C87" s="194"/>
+      <c r="D87" s="194"/>
+      <c r="E87" s="194"/>
+      <c r="F87" s="195"/>
+      <c r="G87" s="196"/>
+      <c r="R87" s="205" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
+      <c r="A88" s="193">
+        <v>83</v>
+      </c>
+      <c r="B88" s="194"/>
+      <c r="C88" s="194"/>
+      <c r="D88" s="194"/>
+      <c r="E88" s="194"/>
+      <c r="F88" s="195"/>
+      <c r="G88" s="196"/>
+      <c r="R88" s="205" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
+      <c r="A89" s="193">
+        <v>84</v>
+      </c>
+      <c r="B89" s="194"/>
+      <c r="C89" s="194"/>
+      <c r="D89" s="194"/>
+      <c r="E89" s="194"/>
+      <c r="F89" s="195"/>
+      <c r="G89" s="196"/>
+      <c r="R89" s="205" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
+      <c r="A90" s="193">
+        <v>85</v>
+      </c>
+      <c r="B90" s="194"/>
+      <c r="C90" s="194"/>
+      <c r="D90" s="194"/>
+      <c r="E90" s="194"/>
+      <c r="F90" s="195"/>
+      <c r="G90" s="196"/>
+      <c r="R90" s="205" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
+      <c r="A91" s="193">
+        <v>86</v>
+      </c>
+      <c r="B91" s="194"/>
+      <c r="C91" s="194"/>
+      <c r="D91" s="194"/>
+      <c r="E91" s="194"/>
+      <c r="F91" s="195"/>
+      <c r="G91" s="196"/>
+      <c r="R91" s="205" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
+      <c r="A92" s="193">
+        <v>87</v>
+      </c>
+      <c r="B92" s="194"/>
+      <c r="C92" s="194"/>
+      <c r="D92" s="194"/>
+      <c r="E92" s="194"/>
+      <c r="F92" s="195"/>
+      <c r="G92" s="196"/>
+      <c r="R92" s="205" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
+      <c r="A93" s="193">
+        <v>88</v>
+      </c>
+      <c r="B93" s="194"/>
+      <c r="C93" s="194"/>
+      <c r="D93" s="194"/>
+      <c r="E93" s="194"/>
+      <c r="F93" s="195"/>
+      <c r="G93" s="196"/>
+      <c r="R93" s="205" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
+      <c r="A94" s="193">
+        <v>89</v>
+      </c>
+      <c r="B94" s="194"/>
+      <c r="C94" s="194"/>
+      <c r="D94" s="194"/>
+      <c r="E94" s="194"/>
+      <c r="F94" s="195"/>
+      <c r="G94" s="196"/>
+      <c r="R94" s="205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
+      <c r="A95" s="193">
+        <v>90</v>
+      </c>
+      <c r="B95" s="194"/>
+      <c r="C95" s="194"/>
+      <c r="D95" s="194"/>
+      <c r="E95" s="194"/>
+      <c r="F95" s="195"/>
+      <c r="G95" s="196"/>
+      <c r="R95" s="205" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
+      <c r="A96" s="193">
+        <v>91</v>
+      </c>
+      <c r="B96" s="194"/>
+      <c r="C96" s="194"/>
+      <c r="D96" s="194"/>
+      <c r="E96" s="194"/>
+      <c r="F96" s="195"/>
+      <c r="G96" s="196"/>
+      <c r="R96" s="205" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
+      <c r="A97" s="193">
+        <v>92</v>
+      </c>
+      <c r="B97" s="194"/>
+      <c r="C97" s="194"/>
+      <c r="D97" s="194"/>
+      <c r="E97" s="194"/>
+      <c r="F97" s="195"/>
+      <c r="G97" s="196"/>
+      <c r="R97" s="205" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
+      <c r="A98" s="193">
+        <v>93</v>
+      </c>
+      <c r="B98" s="194"/>
+      <c r="C98" s="194"/>
+      <c r="D98" s="194"/>
+      <c r="E98" s="194"/>
+      <c r="F98" s="195"/>
+      <c r="G98" s="196"/>
+      <c r="R98" s="205" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
+      <c r="A99" s="193">
+        <v>94</v>
+      </c>
+      <c r="B99" s="194"/>
+      <c r="C99" s="194"/>
+      <c r="D99" s="194"/>
+      <c r="E99" s="194"/>
+      <c r="F99" s="195"/>
+      <c r="G99" s="196"/>
+      <c r="R99" s="205" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
+      <c r="A100" s="193">
+        <v>95</v>
+      </c>
+      <c r="B100" s="194"/>
+      <c r="C100" s="194"/>
+      <c r="D100" s="194"/>
+      <c r="E100" s="194"/>
+      <c r="F100" s="195"/>
+      <c r="G100" s="196"/>
+      <c r="R100" s="205" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
+      <c r="A101" s="193">
+        <v>96</v>
+      </c>
+      <c r="B101" s="194"/>
+      <c r="C101" s="194"/>
+      <c r="D101" s="194"/>
+      <c r="E101" s="194"/>
+      <c r="F101" s="195"/>
+      <c r="G101" s="196"/>
+      <c r="R101" s="205" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
+      <c r="A102" s="193">
+        <v>97</v>
+      </c>
+      <c r="B102" s="194"/>
+      <c r="C102" s="194"/>
+      <c r="D102" s="194"/>
+      <c r="E102" s="194"/>
+      <c r="F102" s="195"/>
+      <c r="G102" s="196"/>
+      <c r="R102" s="205" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
+      <c r="A103" s="193">
+        <v>98</v>
+      </c>
+      <c r="B103" s="194"/>
+      <c r="C103" s="194"/>
+      <c r="D103" s="194"/>
+      <c r="E103" s="194"/>
+      <c r="F103" s="195"/>
+      <c r="G103" s="196"/>
+      <c r="R103" s="205" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
+      <c r="A104" s="193">
+        <v>99</v>
+      </c>
+      <c r="B104" s="194"/>
+      <c r="C104" s="194"/>
+      <c r="D104" s="194"/>
+      <c r="E104" s="194"/>
+      <c r="F104" s="195"/>
+      <c r="G104" s="196"/>
+      <c r="R104" s="205" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
+      <c r="A105" s="197">
+        <v>100</v>
+      </c>
+      <c r="B105" s="198"/>
+      <c r="C105" s="198"/>
+      <c r="D105" s="198"/>
+      <c r="E105" s="198"/>
+      <c r="F105" s="199"/>
+      <c r="G105" s="200"/>
+      <c r="R105" s="205" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
+      <c r="R106" s="205" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
+      <c r="R107" s="205" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
+      <c r="R108" s="205" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
+      <c r="R109" s="205" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
+      <c r="R110" s="205" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
+      <c r="R111" s="205" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
+      <c r="R112" s="205" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="113" spans="18:18">
+      <c r="R113" s="205" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="114" spans="18:18">
+      <c r="R114" s="205" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="115" spans="18:18">
+      <c r="R115" s="205" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="116" spans="18:18">
+      <c r="R116" s="205" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="117" spans="18:18">
+      <c r="R117" s="205" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118" spans="18:18">
+      <c r="R118" s="205" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="119" spans="18:18">
+      <c r="R119" s="205" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="120" spans="18:18">
+      <c r="R120" s="205" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="18:18">
+      <c r="R121" s="205" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="122" spans="18:18">
+      <c r="R122" s="205" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="123" spans="18:18">
+      <c r="R123" s="205" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="18:18">
+      <c r="R124" s="205" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="125" spans="18:18">
+      <c r="R125" s="205" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="126" spans="18:18">
+      <c r="R126" s="205" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="127" spans="18:18">
+      <c r="R127" s="205" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="128" spans="18:18">
+      <c r="R128" s="205" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="129" spans="18:18">
+      <c r="R129" s="205" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="130" spans="18:18">
+      <c r="R130" s="205" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="131" spans="18:18">
+      <c r="R131" s="205" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="132" spans="18:18">
+      <c r="R132" s="205" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="133" spans="18:18">
+      <c r="R133" s="205" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="134" spans="18:18">
+      <c r="R134" s="205" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="135" spans="18:18">
+      <c r="R135" s="205" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="136" spans="18:18">
+      <c r="R136" s="205" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="137" spans="18:18">
+      <c r="R137" s="205" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="138" spans="18:18">
+      <c r="R138" s="205" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="139" spans="18:18">
+      <c r="R139" s="205" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="140" spans="18:18">
+      <c r="R140" s="205" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="141" spans="18:18">
+      <c r="R141" s="205" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="142" spans="18:18">
+      <c r="R142" s="205" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="143" spans="18:18">
+      <c r="R143" s="205" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="144" spans="18:18">
+      <c r="R144" s="205" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="145" spans="18:18">
+      <c r="R145" s="205" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="146" spans="18:18">
+      <c r="R146" s="205" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="147" spans="18:18">
+      <c r="R147" s="205" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="148" spans="18:18">
+      <c r="R148" s="205" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="149" spans="18:18">
+      <c r="R149" s="205" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="150" spans="18:18">
+      <c r="R150" s="205" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="151" spans="18:18">
+      <c r="R151" s="205" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="152" spans="18:18">
+      <c r="R152" s="205" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="153" spans="18:18">
+      <c r="R153" s="205" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="154" spans="18:18">
+      <c r="R154" s="205" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="155" spans="18:18">
+      <c r="R155" s="205" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="156" spans="18:18">
+      <c r="R156" s="205" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="157" spans="18:18">
+      <c r="R157" s="205" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="158" spans="18:18">
+      <c r="R158" s="205" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="159" spans="18:18">
+      <c r="R159" s="205" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="160" spans="18:18">
+      <c r="R160" s="205" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="161" spans="18:18">
+      <c r="R161" s="205" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="162" spans="18:18">
+      <c r="R162" s="205" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="163" spans="18:18">
+      <c r="R163" s="205" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="164" spans="18:18">
+      <c r="R164" s="205" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="165" spans="18:18">
+      <c r="R165" s="205" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="166" spans="18:18">
+      <c r="R166" s="205" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="167" spans="18:18">
+      <c r="R167" s="205" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="168" spans="18:18">
+      <c r="R168" s="205" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="169" spans="18:18">
+      <c r="R169" s="205" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="170" spans="18:18">
+      <c r="R170" s="205" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="171" spans="18:18">
+      <c r="R171" s="205" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="172" spans="18:18">
+      <c r="R172" s="205" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="173" spans="18:18">
+      <c r="R173" s="205" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="174" spans="18:18">
+      <c r="R174" s="205" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="175" spans="18:18">
+      <c r="R175" s="205" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="176" spans="18:18">
+      <c r="R176" s="205" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="177" spans="18:18">
+      <c r="R177" s="205" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="178" spans="18:18">
+      <c r="R178" s="205" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="179" spans="18:18">
+      <c r="R179" s="205" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="180" spans="18:18">
+      <c r="R180" s="205" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="181" spans="18:18">
+      <c r="R181" s="205" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="182" spans="18:18">
+      <c r="R182" s="205" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="183" spans="18:18">
+      <c r="R183" s="205" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="184" spans="18:18">
+      <c r="R184" s="205" t="s">
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="A028" sheet="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6:E105">
+      <formula1>LTV_ref</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D6:D105">
+      <formula1>Norm_ref</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C6:C105">
+      <formula1>CurrCode_ref</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6:B105">
+      <formula1>Loan_ref</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/v03.xlsx
+++ b/v03.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\9da9746c-e37d-42f7-9afe-763929a2622e\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\host.lan\Data\files\tasks\b474dad2-b3c0-4713-88b3-9fb7a1aa288e\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DC34F43-2C27-4889-9180-3312A6EC6DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F696D76-8BA3-4A3B-96F3-470C496DD7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookPassword="C085" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10440" tabRatio="601" activeTab="6"/>
